--- a/output/pdf_financials_xlsx/BCU.xlsx
+++ b/output/pdf_financials_xlsx/BCU.xlsx
@@ -1327,16 +1327,16 @@
         <v>-0.810066</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-1.518869</v>
@@ -1643,16 +1643,16 @@
         <v>-0.810066</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.518869</v>
@@ -1826,16 +1826,16 @@
         <v>-0.810066</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-1.518869</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>37.45145</v>
+        <v>-37.45145</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2082,16 +2082,16 @@
         <v>-0.810066</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.518869</v>
@@ -2204,16 +2204,16 @@
         <v>-0.810066</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.518869</v>
@@ -2362,16 +2362,16 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6575,7 +6575,7 @@
         <v>-1.518869</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>1.600627</v>
+        <v>-1.600627</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-2.337617</v>
@@ -7701,52 +7701,52 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-2.048697</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-2.430527</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>6.751257</v>
+        <v>5.827438</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.254057</v>
+        <v>0.180651</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.056867</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.082054</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.067431</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.598514</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.380197</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001305</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.4741</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.594065</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-1.440247</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004162</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.24768</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.527853</v>
       </c>
     </row>
     <row r="119">
@@ -25939,7 +25939,7 @@
         </is>
       </c>
       <c r="R164" s="5" t="n">
-        <v>1.600627</v>
+        <v>-1.600627</v>
       </c>
       <c r="S164" s="5" t="n">
         <v>-2.337617</v>
@@ -26638,7 +26638,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -28718,7 +28722,11 @@
           <t>Accounts payable included in exploration and evaluation asset expenditures $</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -43215,7 +43223,7 @@
         </is>
       </c>
       <c r="J331" s="5" t="n">
-        <v>8.423387999999999</v>
+        <v>-8.423387999999999</v>
       </c>
       <c r="K331" s="5" t="n">
         <v>-0.560301</v>
@@ -48252,7 +48260,11 @@
           <t>Loss on impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -59911,16 +59923,16 @@
         </is>
       </c>
       <c r="N490" s="5" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="O490" s="5" t="n">
-        <v>0.614622</v>
+        <v>-0.614622</v>
       </c>
       <c r="P490" s="5" t="n">
-        <v>0.265076</v>
+        <v>-0.265076</v>
       </c>
       <c r="Q490" s="5" t="n">
-        <v>1.518869</v>
+        <v>-1.518869</v>
       </c>
       <c r="R490" t="inlineStr">
         <is>
@@ -62410,13 +62422,13 @@
         </is>
       </c>
       <c r="O514" s="5" t="n">
-        <v>0.476316</v>
+        <v>-0.476316</v>
       </c>
       <c r="P514" s="5" t="n">
-        <v>0.186829</v>
+        <v>-0.186829</v>
       </c>
       <c r="Q514" s="5" t="n">
-        <v>1.512053</v>
+        <v>-1.512053</v>
       </c>
       <c r="R514" t="inlineStr">
         <is>
@@ -63339,10 +63351,10 @@
         </is>
       </c>
       <c r="N523" s="5" t="n">
-        <v>0.835421</v>
+        <v>-0.835421</v>
       </c>
       <c r="O523" s="5" t="n">
-        <v>0.476316</v>
+        <v>-0.476316</v>
       </c>
       <c r="P523" t="inlineStr">
         <is>
@@ -63970,10 +63982,10 @@
         </is>
       </c>
       <c r="M529" s="5" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="N529" s="5" t="n">
-        <v>0.7490289999999999</v>
+        <v>-0.7490289999999999</v>
       </c>
       <c r="O529" t="inlineStr">
         <is>
@@ -64184,10 +64196,10 @@
         </is>
       </c>
       <c r="M531" s="5" t="n">
-        <v>0.186996</v>
+        <v>-0.186996</v>
       </c>
       <c r="N531" s="5" t="n">
-        <v>0.835421</v>
+        <v>-0.835421</v>
       </c>
       <c r="O531" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BCU.xlsx
+++ b/output/pdf_financials_xlsx/BCU.xlsx
@@ -943,25 +943,25 @@
         <v>4.548693</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6.46963</v>
+        <v>4.921029</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.618101</v>
+        <v>5.652113</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.962265</v>
+        <v>2.550969</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.24905</v>
+        <v>1.696155</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.144523</v>
+        <v>0.560301</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.156607</v>
+        <v>0.804565</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.155016</v>
+        <v>0.186996</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.231675</v>
@@ -1004,25 +1004,25 @@
         <v>-1.890252</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-6.46963</v>
+        <v>-4.921029</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.618101</v>
+        <v>-5.652113</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.962265</v>
+        <v>-2.550969</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.24905</v>
+        <v>-1.696155</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.144523</v>
+        <v>-0.560301</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.156607</v>
+        <v>-0.804565</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.155016</v>
+        <v>-0.186996</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.231675</v>
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003069</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00389</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004279</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2064,13 +2064,13 @@
         <v>-4.545545</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.889607</v>
+        <v>-5.886538</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.565708</v>
+        <v>-5.561818</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-43.583624</v>
+        <v>-43.587903</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>8.423387999999999</v>
@@ -2186,13 +2186,13 @@
         <v>-4.545545</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.875752</v>
+        <v>-5.872683</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.559081</v>
+        <v>-5.555191</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-43.577506</v>
+        <v>-43.581785</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.423387999999999</v>
@@ -2512,49 +2512,49 @@
         <v>0.25248</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.453964</v>
+        <v>0.504419</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.04006</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.059363</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011655</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002804</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.336337</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.211803</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.075002</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.153164</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.324845</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.191062</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.057364</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.011678</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.004382</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.00037</v>
       </c>
     </row>
     <row r="35">
@@ -2634,49 +2634,49 @@
         <v>0.285731</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.479714</v>
+        <v>0.530169</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.04006</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.059363</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011655</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002804</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.336337</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.211803</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.075002</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.153164</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.324845</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.191062</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.057364</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.011678</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.004382</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.00037</v>
       </c>
     </row>
     <row r="37">
@@ -3366,49 +3366,49 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.06479799999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.114472</v>
+        <v>0.07441200000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.068</v>
+        <v>0.008637000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.01653</v>
+        <v>0.004875</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.002804</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.336337</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.211803</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.075002</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.153164</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.324845</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.191062</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.192804</v>
+        <v>0.13544</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.019742</v>
+        <v>0.008064</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.021207</v>
+        <v>0.016825</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.015085</v>
+        <v>0.014715</v>
       </c>
     </row>
     <row r="49">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -64580,7 +64580,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -64600,19 +64600,19 @@
         <v>5.652113</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>-2.550969</v>
+        <v>2.550969</v>
       </c>
       <c r="J535" s="5" t="n">
-        <v>-1.696155</v>
+        <v>1.696155</v>
       </c>
       <c r="K535" s="5" t="n">
-        <v>-0.560301</v>
+        <v>0.560301</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>-0.804565</v>
+        <v>0.804565</v>
       </c>
       <c r="M535" s="5" t="n">
-        <v>-0.186996</v>
+        <v>0.186996</v>
       </c>
       <c r="N535" t="inlineStr">
         <is>
@@ -67938,7 +67938,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -74740,7 +74740,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E631" s="5" t="n">

--- a/output/pdf_financials_xlsx/BCU.xlsx
+++ b/output/pdf_financials_xlsx/BCU.xlsx
@@ -1312,10 +1312,10 @@
         <v>-5.889607</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-5.565708</v>
+        <v>-5.455708</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-43.583624</v>
+        <v>-32.493624</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>8.423387999999999</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.129929</v>
+        <v>-0.129929</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>4.548693</v>
@@ -1373,10 +1373,10 @@
         <v>6.46963</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.11</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-11.09</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -2067,10 +2067,10 @@
         <v>-5.886538</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.561818</v>
+        <v>-5.451818</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-43.587903</v>
+        <v>-32.497903</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>8.423387999999999</v>
@@ -2189,10 +2189,10 @@
         <v>-5.872683</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.555191</v>
+        <v>-5.445191</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-43.581785</v>
+        <v>-32.491785</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.423387999999999</v>
@@ -2347,10 +2347,10 @@
         <v>-109.8482462412178</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.01623693936699</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-34.12977265939927</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -4569,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.080813</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.09503</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -6670,46 +6670,46 @@
         <v>-0.120653</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.028903</v>
+        <v>0.039116</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.052705</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005144</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.013491</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005594</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.002157</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.003338</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007268</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.008795000000000001</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01333</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.012246</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.000512</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0</v>
+        <v>0.000155</v>
       </c>
     </row>
     <row r="102">
@@ -6975,46 +6975,46 @@
         <v>-0.583739</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.329401</v>
+        <v>-0.261382</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.120873</v>
+        <v>-0.06816800000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.286075</v>
+        <v>0.280931</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.126922</v>
+        <v>-0.113431</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.374464</v>
+        <v>0.36887</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.087075</v>
+        <v>-0.08491799999999999</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.19284</v>
+        <v>-0.189502</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.115615</v>
+        <v>0.108347</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.016977</v>
+        <v>-0.008182</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.418541</v>
+        <v>-0.431871</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.646827</v>
+        <v>-0.634581</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.346975</v>
+        <v>0.347487</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.249972</v>
+        <v>0.250035</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>0.891205</v>
+        <v>0.89136</v>
       </c>
     </row>
     <row r="107">
@@ -7307,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025836</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7512,16 +7512,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.484984</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.187855</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.02155</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025836</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
         <v>-0.391966</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.569454</v>
+        <v>-0.59529</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-1.276739</v>
@@ -26450,7 +26450,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -32298,7 +32302,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -32510,7 +32518,11 @@
           <t>Proceeds of shares issued for cash</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -36554,7 +36566,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -48690,7 +48706,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -51124,7 +51144,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -52178,7 +52202,11 @@
           <t>- future income tax recovery</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -56322,7 +56350,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E455" s="5" t="n">
         <v>-0.129929</v>
       </c>
@@ -57692,7 +57724,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E468" s="5" t="n">
         <v>0.484984</v>
       </c>
@@ -69202,7 +69238,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -70472,7 +70512,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -72386,7 +72430,11 @@
           <t>Future income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E609" t="inlineStr">
         <is>
           <t>-</t>
@@ -76006,7 +76054,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E643" s="5" t="n">
         <v>0.129929</v>
       </c>
